--- a/artfynd/A 20863-2024 artfynd.xlsx
+++ b/artfynd/A 20863-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117894740</v>
+        <v>117894771</v>
       </c>
       <c r="B2" t="n">
-        <v>97756</v>
+        <v>96793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>224363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -783,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117894771</v>
+        <v>117894740</v>
       </c>
       <c r="B3" t="n">
-        <v>96793</v>
+        <v>97756</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,16 +799,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224363</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>

--- a/artfynd/A 20863-2024 artfynd.xlsx
+++ b/artfynd/A 20863-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117894771</v>
+        <v>117894740</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>97758</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>223597</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -783,10 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117894740</v>
+        <v>117894771</v>
       </c>
       <c r="B3" t="n">
-        <v>97756</v>
+        <v>96795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,16 +799,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>224363</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
+          <t>Lycopodium annotinum subsp. annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
